--- a/Post-cursada/Tiempos x tarea Post Cursada - Kairos - NexTech.xlsx
+++ b/Post-cursada/Tiempos x tarea Post Cursada - Kairos - NexTech.xlsx
@@ -3,9 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Hoja 2" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Hoja 3" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Cierre" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Iteracion 1 " sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Iteracion 2" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Iteracion 3" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,51 +14,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="24">
+  <si>
+    <t>Cierre: 19/11/25 - 28/11/25</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Propietario</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Fecha inicio plan</t>
+  </si>
+  <si>
+    <t>Fecha fin plan</t>
+  </si>
+  <si>
+    <t>Fecha inicio real</t>
+  </si>
+  <si>
+    <t>Fecha fin real</t>
+  </si>
+  <si>
+    <t>Duración estimada</t>
+  </si>
+  <si>
+    <t>Tiempo registrado</t>
+  </si>
+  <si>
+    <t>Notas</t>
+  </si>
+  <si>
+    <t>Grabar y editar video vista admin manual de usuario</t>
+  </si>
+  <si>
+    <t>Documentación</t>
+  </si>
+  <si>
+    <t>Agustina Maldonado</t>
+  </si>
+  <si>
+    <t>Sin comenzar</t>
+  </si>
+  <si>
+    <t>Grabar y editar video vista miembro manual de usuario</t>
+  </si>
+  <si>
+    <t>En curso</t>
+  </si>
+  <si>
+    <t>Grabar y editar video vista lider manual de usuario</t>
+  </si>
   <si>
     <t>Iteración 1: 18/12/25 - 22/12/25</t>
   </si>
   <si>
-    <t>Tarea</t>
-  </si>
-  <si>
-    <t>Categoría</t>
-  </si>
-  <si>
-    <t>Propietario</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Fecha inicio plan</t>
-  </si>
-  <si>
-    <t>Fecha fin plan</t>
-  </si>
-  <si>
-    <t>Fecha inicio real</t>
-  </si>
-  <si>
-    <t>Fecha fin real</t>
-  </si>
-  <si>
-    <t>Duración estimada</t>
-  </si>
-  <si>
-    <t>Tiempo registrado</t>
-  </si>
-  <si>
-    <t>Notas</t>
-  </si>
-  <si>
     <t>Revisión de documentos en búsqueda de inconsistencias</t>
   </si>
   <si>
     <t>Corrección de documentos</t>
   </si>
   <si>
-    <t>Iteración 2: ##/01/26 - ##/02/26</t>
+    <t>Iteración 2: 20/01/26 - 03/02/26</t>
   </si>
   <si>
     <t>Iteración 3: ##/02/26 - ##/02/26</t>
@@ -70,7 +95,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/M/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -83,6 +108,18 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -108,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -122,19 +159,31 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -204,20 +253,26 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="3">
-    <tableStyle count="4" pivot="0" name="Hoja 1-style">
+  <tableStyles count="4">
+    <tableStyle count="4" pivot="0" name="Cierre-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Hoja 2-style">
+    <tableStyle count="4" pivot="0" name="Iteracion 1 -style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Hoja 3-style">
+    <tableStyle count="4" pivot="0" name="Iteracion 2-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="Iteracion 3-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -239,8 +294,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_1" name="Tabla_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K9" displayName="Tabla_4" name="Tabla_4" id="1">
   <tableColumns count="11">
     <tableColumn name="Tarea" id="1"/>
     <tableColumn name="Categoría" id="2"/>
@@ -254,12 +313,12 @@
     <tableColumn name="Tiempo registrado" id="10"/>
     <tableColumn name="Notas" id="11"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Cierre-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_2" name="Tabla_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_1" name="Tabla_1" id="2">
   <tableColumns count="11">
     <tableColumn name="Tarea" id="1"/>
     <tableColumn name="Categoría" id="2"/>
@@ -273,12 +332,12 @@
     <tableColumn name="Tiempo registrado" id="10"/>
     <tableColumn name="Notas" id="11"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 2-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Iteracion 1 -style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_3" name="Tabla_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_2" name="Tabla_2" id="3">
   <tableColumns count="11">
     <tableColumn name="Tarea" id="1"/>
     <tableColumn name="Categoría" id="2"/>
@@ -292,7 +351,26 @@
     <tableColumn name="Tiempo registrado" id="10"/>
     <tableColumn name="Notas" id="11"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 3-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Iteracion 2-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_3" name="Tabla_3" id="4">
+  <tableColumns count="11">
+    <tableColumn name="Tarea" id="1"/>
+    <tableColumn name="Categoría" id="2"/>
+    <tableColumn name="Propietario" id="3"/>
+    <tableColumn name="Estado" id="4"/>
+    <tableColumn name="Fecha inicio plan" id="5"/>
+    <tableColumn name="Fecha fin plan" id="6"/>
+    <tableColumn name="Fecha inicio real" id="7"/>
+    <tableColumn name="Fecha fin real" id="8"/>
+    <tableColumn name="Duración estimada" id="9"/>
+    <tableColumn name="Tiempo registrado" id="10"/>
+    <tableColumn name="Notas" id="11"/>
+  </tableColumns>
+  <tableStyleInfo name="Iteracion 3-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -497,10 +575,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="29.25"/>
-    <col customWidth="1" min="2" max="2" width="16.88"/>
-    <col customWidth="1" min="4" max="4" width="15.25"/>
-    <col customWidth="1" min="9" max="9" width="12.25"/>
+    <col customWidth="1" min="1" max="1" width="24.5"/>
+    <col customWidth="1" min="2" max="2" width="17.63"/>
+    <col customWidth="1" min="3" max="3" width="15.75"/>
+    <col customWidth="1" min="4" max="4" width="19.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,174 +625,136 @@
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="G5" s="12">
+        <v>45985.0</v>
+      </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="9"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="15"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="7"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="9"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="15"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="6"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="15"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="9"/>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="9"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K2"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D14">
+    <dataValidation type="list" allowBlank="1" sqref="D4:D9">
       <formula1>"Sin comenzar,En curso,Bloqueado,Completado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B4:B14">
+    <dataValidation type="list" allowBlank="1" sqref="B4:B9">
       <formula1>"Análisis,Documentación,Codificación,Validación y Verificación,Diseño,Actividades Externas,Capacitación,Pruebas"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F9">
       <formula1>OR(NOT(ISERROR(DATEVALUE(E4))), AND(ISNUMBER(E4), LEFT(CELL("format", E4))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I9">
       <formula1>AND(ISNUMBER(I4),(NOT(OR(NOT(ISERROR(DATEVALUE(I4))), AND(ISNUMBER(I4), LEFT(CELL("format", I4))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H9">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G4))), AND(ISNUMBER(G4), LEFT(CELL("format", G4))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A14 J4:J14"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A9 J4:J9"/>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C4"/>
+    <hyperlink r:id="rId2" ref="C5"/>
+    <hyperlink r:id="rId3" ref="C6"/>
+  </hyperlinks>
+  <drawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -734,7 +774,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -774,148 +814,150 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="15"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="15"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="15"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="9"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="15"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="7"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="9"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="15"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="6"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="15"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="15"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="7"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="15"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="15"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="15"/>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="15"/>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -961,7 +1003,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -1000,149 +1042,372 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="15"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="15"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="15"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="9"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="15"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="7"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="9"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="15"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="6"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="15"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="15"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="7"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="15"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="15"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="15"/>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="15"/>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K2"/>
+  </mergeCells>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" sqref="D4:D14">
+      <formula1>"Sin comenzar,En curso,Bloqueado,Completado"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B4:B14">
+      <formula1>"Análisis,Documentación,Codificación,Validación y Verificación,Diseño,Actividades Externas,Capacitación,Pruebas"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F14">
+      <formula1>OR(NOT(ISERROR(DATEVALUE(E4))), AND(ISNUMBER(E4), LEFT(CELL("format", E4))="D"))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I14">
+      <formula1>AND(ISNUMBER(I4),(NOT(OR(NOT(ISERROR(DATEVALUE(I4))), AND(ISNUMBER(I4), LEFT(CELL("format", I4))="D")))))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H14">
+      <formula1>OR(NOT(ISERROR(DATEVALUE(G4))), AND(ISNUMBER(G4), LEFT(CELL("format", G4))="D"))</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A14 J4:J14"/>
+  </dataValidations>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="29.25"/>
+    <col customWidth="1" min="2" max="2" width="16.88"/>
+    <col customWidth="1" min="4" max="4" width="15.25"/>
+    <col customWidth="1" min="9" max="9" width="12.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Post-cursada/Tiempos x tarea Post Cursada - Kairos - NexTech.xlsx
+++ b/Post-cursada/Tiempos x tarea Post Cursada - Kairos - NexTech.xlsx
@@ -3,10 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Cierre" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Iteracion 1 " sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Iteracion 2" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Iteracion 3" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Iteracion 1 " sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Iteracion 2" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Iteracion 3" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Cierre" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,78 +14,294 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="96">
+  <si>
+    <t>Iteración 1: 18/12/25 - 22/12/25</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Propietario</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Fecha inicio plan</t>
+  </si>
+  <si>
+    <t>Fecha fin plan</t>
+  </si>
+  <si>
+    <t>Fecha inicio real</t>
+  </si>
+  <si>
+    <t>Fecha fin real</t>
+  </si>
+  <si>
+    <t>Duración estimada</t>
+  </si>
+  <si>
+    <t>Tiempo registrado</t>
+  </si>
+  <si>
+    <t>Notas</t>
+  </si>
+  <si>
+    <t>Implementación CU02 Exportar Información.</t>
+  </si>
+  <si>
+    <t>Codificación</t>
+  </si>
+  <si>
+    <t>guilleh114@gmail.com</t>
+  </si>
+  <si>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>10h</t>
+  </si>
+  <si>
+    <t>8.25h</t>
+  </si>
+  <si>
+    <t>Revisión de documentos en búsqueda de inconsistencias y errores.</t>
+  </si>
+  <si>
+    <t>Validación y Verificación</t>
+  </si>
+  <si>
+    <t>Agustina Maldonado</t>
+  </si>
+  <si>
+    <t>En curso</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>Documentar revisión</t>
+  </si>
+  <si>
+    <t>Documentación</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>Corrección de defectos en documentos.</t>
+  </si>
+  <si>
+    <t>Sin comenzar</t>
+  </si>
+  <si>
+    <t>3.5 hs</t>
+  </si>
+  <si>
+    <t>Revisión de correcciones y aprobación de los documentos.</t>
+  </si>
+  <si>
+    <t>gonzalo.ulloa99@gmail.com</t>
+  </si>
+  <si>
+    <t>1 hs</t>
+  </si>
+  <si>
+    <t>Ejecución de casos de prueba para el CU02 Exportar Información.</t>
+  </si>
+  <si>
+    <t>Pruebas</t>
+  </si>
+  <si>
+    <t>esstefaniamendez@gmail.com</t>
+  </si>
+  <si>
+    <t>1 h</t>
+  </si>
+  <si>
+    <t>Funcionalidades extras en el CU22: Ver Reporte</t>
+  </si>
+  <si>
+    <t>vale</t>
+  </si>
+  <si>
+    <t>4hs</t>
+  </si>
+  <si>
+    <t>40m</t>
+  </si>
+  <si>
+    <t>Ejecución de casos de pruebas en funcionalidades extras CU22: Ver reporte</t>
+  </si>
+  <si>
+    <t>3hs</t>
+  </si>
+  <si>
+    <t>Refinar planificación iteracion 2</t>
+  </si>
+  <si>
+    <t>Actividades Externas</t>
+  </si>
+  <si>
+    <t>25min</t>
+  </si>
+  <si>
+    <t>Recordar especificar tareas correspondientes al desarrollo de la memoria</t>
+  </si>
+  <si>
+    <t>Preparar información y documentación para la memoria</t>
+  </si>
+  <si>
+    <t>Manual de usuario dentro del sistema kairos</t>
+  </si>
+  <si>
+    <t>Valeria Centurion</t>
+  </si>
+  <si>
+    <t>5:00h</t>
+  </si>
+  <si>
+    <t>Iteración 2: 20/01/26 - 03/02/26</t>
+  </si>
+  <si>
+    <t>Estimación Iteración 2</t>
+  </si>
+  <si>
+    <t>Análisis</t>
+  </si>
+  <si>
+    <t>centurionvaleria6@gmail.com</t>
+  </si>
+  <si>
+    <t>Gestión de riesgos</t>
+  </si>
+  <si>
+    <t>Revisar y documentar errores en documentos de la etapa de Elaboración I1</t>
+  </si>
+  <si>
+    <t>Revisar y documentar errores en documentos de la etapa de Elaboración I2</t>
+  </si>
+  <si>
+    <t>2.5hs</t>
+  </si>
+  <si>
+    <t>Terminar manual de instalación</t>
+  </si>
+  <si>
+    <t>Revisar y documentar errores en documentos de la etapa de Construcción I1</t>
+  </si>
+  <si>
+    <t>30 min</t>
+  </si>
+  <si>
+    <t>Revisar y documentar errores en documentos de la etapa de Construcción I2</t>
+  </si>
+  <si>
+    <t>1hs</t>
+  </si>
+  <si>
+    <t>Revisar y documentar errores en documentos de la etapa de Construcción I3</t>
+  </si>
+  <si>
+    <t>Fraccionar Manual de usuario en funcionalidades</t>
+  </si>
+  <si>
+    <t>30min</t>
+  </si>
+  <si>
+    <t>Grabar y editar videos faltantes del Manual de usuario</t>
+  </si>
+  <si>
+    <t>8hs</t>
+  </si>
+  <si>
+    <t>Escribir texto de apoyo para funcionalidades Manual de usuario</t>
+  </si>
+  <si>
+    <t>2hs</t>
+  </si>
+  <si>
+    <t>Revisar texto y contenido audiovisual del Manual de usuario</t>
+  </si>
+  <si>
+    <t>Implementación del Manual de usuario en el sistema Kairos</t>
+  </si>
+  <si>
+    <t>Revisión de la implementación del manual de usuario</t>
+  </si>
+  <si>
+    <t>Ejecución casos prueba CU: 10 - 11</t>
+  </si>
+  <si>
+    <t>Revisar documentos y corregir errores encontrados</t>
+  </si>
+  <si>
+    <t>Florencia Mendez</t>
+  </si>
+  <si>
+    <t>3:00:37</t>
+  </si>
+  <si>
+    <t>No planificado</t>
+  </si>
+  <si>
+    <t>Solicitar de reunión / Presentación de avance</t>
+  </si>
+  <si>
+    <t>Iteración 3: ##/14/02 - ##/02/26</t>
+  </si>
+  <si>
+    <t>3:17:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO CORRESPONDE A ITERACIÓN </t>
+  </si>
+  <si>
+    <t>0:27:32</t>
+  </si>
+  <si>
+    <t>2:16:01</t>
+  </si>
+  <si>
+    <t>3:01:08</t>
+  </si>
   <si>
     <t>Cierre: 19/11/25 - 28/11/25</t>
   </si>
   <si>
-    <t>Tarea</t>
-  </si>
-  <si>
-    <t>Categoría</t>
-  </si>
-  <si>
-    <t>Propietario</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Fecha inicio plan</t>
-  </si>
-  <si>
-    <t>Fecha fin plan</t>
-  </si>
-  <si>
-    <t>Fecha inicio real</t>
-  </si>
-  <si>
-    <t>Fecha fin real</t>
-  </si>
-  <si>
-    <t>Duración estimada</t>
-  </si>
-  <si>
-    <t>Tiempo registrado</t>
-  </si>
-  <si>
-    <t>Notas</t>
+    <t>Planificar Iteración 1 post cursada</t>
+  </si>
+  <si>
+    <t>Planificar Iteración 2 post cursada</t>
+  </si>
+  <si>
+    <t>Planificar Iteración 3 post cursada</t>
+  </si>
+  <si>
+    <t>Estructura de la memoria</t>
+  </si>
+  <si>
+    <t>Manual de Instalación preliminar</t>
   </si>
   <si>
     <t>Grabar y editar video vista admin manual de usuario</t>
   </si>
   <si>
-    <t>Documentación</t>
-  </si>
-  <si>
-    <t>Agustina Maldonado</t>
-  </si>
-  <si>
-    <t>Sin comenzar</t>
-  </si>
-  <si>
     <t>Grabar y editar video vista miembro manual de usuario</t>
   </si>
   <si>
-    <t>En curso</t>
+    <t>06:37:00</t>
   </si>
   <si>
     <t>Grabar y editar video vista lider manual de usuario</t>
-  </si>
-  <si>
-    <t>Iteración 1: 18/12/25 - 22/12/25</t>
-  </si>
-  <si>
-    <t>Revisión de documentos en búsqueda de inconsistencias</t>
-  </si>
-  <si>
-    <t>Corrección de documentos</t>
-  </si>
-  <si>
-    <t>Iteración 2: 20/01/26 - 03/02/26</t>
-  </si>
-  <si>
-    <t>Iteración 3: ##/02/26 - ##/02/26</t>
   </si>
 </sst>
 </file>
@@ -95,7 +311,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/M/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -111,6 +327,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -145,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -155,44 +376,71 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -253,13 +501,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="4">
-    <tableStyle count="4" pivot="0" name="Cierre-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
+  <tableStyles count="5">
     <tableStyle count="4" pivot="0" name="Iteracion 1 -style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -273,6 +515,18 @@
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
     <tableStyle count="4" pivot="0" name="Iteracion 3-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="Iteracion 3-style 2">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="Cierre-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -298,27 +552,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K9" displayName="Tabla_4" name="Tabla_4" id="1">
-  <tableColumns count="11">
-    <tableColumn name="Tarea" id="1"/>
-    <tableColumn name="Categoría" id="2"/>
-    <tableColumn name="Propietario" id="3"/>
-    <tableColumn name="Estado" id="4"/>
-    <tableColumn name="Fecha inicio plan" id="5"/>
-    <tableColumn name="Fecha fin plan" id="6"/>
-    <tableColumn name="Fecha inicio real" id="7"/>
-    <tableColumn name="Fecha fin real" id="8"/>
-    <tableColumn name="Duración estimada" id="9"/>
-    <tableColumn name="Tiempo registrado" id="10"/>
-    <tableColumn name="Notas" id="11"/>
-  </tableColumns>
-  <tableStyleInfo name="Cierre-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_1" name="Tabla_1" id="2">
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K15" displayName="Tabla_1" name="Tabla_1" id="1">
   <tableColumns count="11">
     <tableColumn name="Tarea" id="1"/>
     <tableColumn name="Categoría" id="2"/>
@@ -336,8 +575,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_2" name="Tabla_2" id="3">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K20" displayName="Tabla_2" name="Tabla_2" id="2">
   <tableColumns count="11">
     <tableColumn name="Tarea" id="1"/>
     <tableColumn name="Categoría" id="2"/>
@@ -355,8 +594,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_3" name="Tabla_3" id="4">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K14" displayName="Tabla_3" name="Tabla_3" id="3">
   <tableColumns count="11">
     <tableColumn name="Tarea" id="1"/>
     <tableColumn name="Categoría" id="2"/>
@@ -371,6 +610,44 @@
     <tableColumn name="Notas" id="11"/>
   </tableColumns>
   <tableStyleInfo name="Iteracion 3-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A18:K21" displayName="Tabla_5" name="Tabla_5" id="4">
+  <tableColumns count="11">
+    <tableColumn name="Tarea" id="1"/>
+    <tableColumn name="Categoría" id="2"/>
+    <tableColumn name="Propietario" id="3"/>
+    <tableColumn name="Estado" id="4"/>
+    <tableColumn name="Fecha inicio plan" id="5"/>
+    <tableColumn name="Fecha fin plan" id="6"/>
+    <tableColumn name="Fecha inicio real" id="7"/>
+    <tableColumn name="Fecha fin real" id="8"/>
+    <tableColumn name="Duración estimada" id="9"/>
+    <tableColumn name="Tiempo registrado" id="10"/>
+    <tableColumn name="Notas" id="11"/>
+  </tableColumns>
+  <tableStyleInfo name="Iteracion 3-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:K11" displayName="Tabla_4" name="Tabla_4" id="5">
+  <tableColumns count="11">
+    <tableColumn name="Tarea" id="1"/>
+    <tableColumn name="Categoría" id="2"/>
+    <tableColumn name="Propietario" id="3"/>
+    <tableColumn name="Estado" id="4"/>
+    <tableColumn name="Fecha inicio plan" id="5"/>
+    <tableColumn name="Fecha fin plan" id="6"/>
+    <tableColumn name="Fecha inicio real" id="7"/>
+    <tableColumn name="Fecha fin real" id="8"/>
+    <tableColumn name="Duración estimada" id="9"/>
+    <tableColumn name="Tiempo registrado" id="10"/>
+    <tableColumn name="Notas" id="11"/>
+  </tableColumns>
+  <tableStyleInfo name="Cierre-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -575,10 +852,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.5"/>
-    <col customWidth="1" min="2" max="2" width="17.63"/>
-    <col customWidth="1" min="3" max="3" width="15.75"/>
-    <col customWidth="1" min="4" max="4" width="19.25"/>
+    <col customWidth="1" min="1" max="1" width="29.25"/>
+    <col customWidth="1" min="2" max="2" width="16.88"/>
+    <col customWidth="1" min="3" max="3" width="13.63"/>
+    <col customWidth="1" min="4" max="4" width="15.25"/>
+    <col customWidth="1" min="9" max="9" width="16.25"/>
+    <col customWidth="1" min="10" max="10" width="13.63"/>
+    <col customWidth="1" min="11" max="11" width="26.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,127 +914,346 @@
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="E4" s="6">
+        <v>46009.0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46012.0</v>
+      </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="K4" s="10"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="12">
-        <v>45985.0</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
+        <v>21</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46009.0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46010.0</v>
+      </c>
+      <c r="G5" s="11">
+        <v>46009.0</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>23</v>
+      </c>
       <c r="K5" s="10"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46009.0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46010.0</v>
+      </c>
+      <c r="G6" s="11">
+        <v>46009.0</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46011.0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46012.0</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46012.0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46012.0</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46012.0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46013.0</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="10"/>
+      <c r="E10" s="6">
+        <v>46011.0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46012.0</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46012.0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46013.0</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="14"/>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="11">
+        <v>46013.0</v>
+      </c>
+      <c r="F12" s="11">
+        <v>46013.0</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="14"/>
+      <c r="K12" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="14"/>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="17">
+        <v>46101.0</v>
+      </c>
+      <c r="F14" s="11">
+        <v>46102.0</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K2"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D9">
+    <dataValidation type="list" allowBlank="1" sqref="D4:D15">
       <formula1>"Sin comenzar,En curso,Bloqueado,Completado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B4:B9">
+    <dataValidation type="list" allowBlank="1" sqref="B4:B15">
       <formula1>"Análisis,Documentación,Codificación,Validación y Verificación,Diseño,Actividades Externas,Capacitación,Pruebas"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F9">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F15">
       <formula1>OR(NOT(ISERROR(DATEVALUE(E4))), AND(ISNUMBER(E4), LEFT(CELL("format", E4))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I9">
-      <formula1>AND(ISNUMBER(I4),(NOT(OR(NOT(ISERROR(DATEVALUE(I4))), AND(ISNUMBER(I4), LEFT(CELL("format", I4))="D")))))</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H9">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H15">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G4))), AND(ISNUMBER(G4), LEFT(CELL("format", G4))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A9 J4:J9"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A15 I4:J15"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C4"/>
     <hyperlink r:id="rId2" ref="C5"/>
     <hyperlink r:id="rId3" ref="C6"/>
+    <hyperlink r:id="rId4" ref="C8"/>
+    <hyperlink r:id="rId5" ref="C9"/>
+    <hyperlink r:id="rId6" ref="C11"/>
+    <hyperlink r:id="rId7" ref="C12"/>
+    <hyperlink r:id="rId8" ref="C13"/>
+    <hyperlink r:id="rId9" ref="C14"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId10"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId12"/>
   </tableParts>
 </worksheet>
 </file>
@@ -769,12 +1268,12 @@
     <col customWidth="1" min="1" max="1" width="29.25"/>
     <col customWidth="1" min="2" max="2" width="16.88"/>
     <col customWidth="1" min="4" max="4" width="15.25"/>
-    <col customWidth="1" min="9" max="9" width="12.25"/>
+    <col customWidth="1" min="9" max="9" width="16.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -814,176 +1313,476 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46042.0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46043.0</v>
+      </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
+        <v>55</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46042.0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46043.0</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="14"/>
       <c r="K5" s="10"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46042.0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46042.0</v>
+      </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="9"/>
+      <c r="I6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="14"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="A7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46042.0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46043.0</v>
+      </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="9"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="14"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46042.0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46047.0</v>
+      </c>
       <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="14"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46043.0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46043.0</v>
+      </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="9"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="14"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="6">
+        <v>46043.0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46044.0</v>
+      </c>
       <c r="G10" s="7"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="9"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="14"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46044.0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46044.0</v>
+      </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9"/>
+      <c r="I11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="14"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="6">
+        <v>46046.0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46046.0</v>
+      </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="9"/>
+      <c r="I12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="14"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="6">
+        <v>46047.0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46048.0</v>
+      </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9"/>
+      <c r="I13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="14"/>
       <c r="K13" s="10"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="6">
+        <v>46049.0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46050.0</v>
+      </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="9"/>
+      <c r="I14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="14"/>
       <c r="K14" s="10"/>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="6">
+        <v>46051.0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46051.0</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="14"/>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="6">
+        <v>46054.0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46056.0</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="6">
+        <v>46056.0</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46056.0</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6">
+        <v>46056.0</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46056.0</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="11">
+        <v>46043.0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>46049.0</v>
+      </c>
+      <c r="I19" s="18"/>
+      <c r="J19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K2"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D14">
+    <dataValidation type="list" allowBlank="1" sqref="D4:D20">
       <formula1>"Sin comenzar,En curso,Bloqueado,Completado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B4:B14">
+    <dataValidation type="list" allowBlank="1" sqref="B4:B20">
       <formula1>"Análisis,Documentación,Codificación,Validación y Verificación,Diseño,Actividades Externas,Capacitación,Pruebas"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F20">
       <formula1>OR(NOT(ISERROR(DATEVALUE(E4))), AND(ISNUMBER(E4), LEFT(CELL("format", E4))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I14">
-      <formula1>AND(ISNUMBER(I4),(NOT(OR(NOT(ISERROR(DATEVALUE(I4))), AND(ISNUMBER(I4), LEFT(CELL("format", I4))="D")))))</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H20">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G4))), AND(ISNUMBER(G4), LEFT(CELL("format", G4))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A14 J4:J14"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A20 I4:J20"/>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C4"/>
+    <hyperlink r:id="rId2" ref="C6"/>
+    <hyperlink r:id="rId3" ref="C7"/>
+    <hyperlink r:id="rId4" ref="C8"/>
+    <hyperlink r:id="rId5" ref="C9"/>
+    <hyperlink r:id="rId6" ref="C10"/>
+    <hyperlink r:id="rId7" ref="C11"/>
+    <hyperlink r:id="rId8" ref="C12"/>
+    <hyperlink r:id="rId9" ref="C13"/>
+    <hyperlink r:id="rId10" ref="C14"/>
+    <hyperlink r:id="rId11" ref="C16"/>
+    <hyperlink r:id="rId12" ref="C18"/>
+    <hyperlink r:id="rId13" ref="C19"/>
+  </hyperlinks>
+  <drawing r:id="rId14"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1003,7 +1802,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -1042,173 +1841,324 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10"/>
+      <c r="A4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="11">
+        <v>46078.0</v>
+      </c>
+      <c r="H4" s="11">
+        <v>46079.0</v>
+      </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="14"/>
       <c r="K5" s="10"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="15"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="9"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="14"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="9"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="14"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="15"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="14"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="9"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="14"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="9"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="14"/>
       <c r="K10" s="10"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="15"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="14"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="9"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="14"/>
       <c r="K12" s="10"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="6"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="14"/>
       <c r="K13" s="10"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="6"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="15"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="9"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="14"/>
       <c r="K14" s="10"/>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="11">
+        <v>46080.0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>46080.0</v>
+      </c>
+      <c r="I19" s="21"/>
+      <c r="J19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="11">
+        <v>46085.0</v>
+      </c>
+      <c r="H20" s="11">
+        <v>46086.0</v>
+      </c>
+      <c r="I20" s="21"/>
+      <c r="J20" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="11">
+        <v>46088.0</v>
+      </c>
+      <c r="H21" s="11">
+        <v>46090.0</v>
+      </c>
+      <c r="I21" s="21"/>
+      <c r="J21" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:K2"/>
+    <mergeCell ref="A16:K17"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D14">
+    <dataValidation type="list" allowBlank="1" sqref="D4:D14 D19:D21">
       <formula1>"Sin comenzar,En curso,Bloqueado,Completado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B4:B14">
+    <dataValidation type="list" allowBlank="1" sqref="B4:B14 B19:B21">
       <formula1>"Análisis,Documentación,Codificación,Validación y Verificación,Diseño,Actividades Externas,Capacitación,Pruebas"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F14 E19:F21">
       <formula1>OR(NOT(ISERROR(DATEVALUE(E4))), AND(ISNUMBER(E4), LEFT(CELL("format", E4))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I14 I19:I21">
       <formula1>AND(ISNUMBER(I4),(NOT(OR(NOT(ISERROR(DATEVALUE(I4))), AND(ISNUMBER(I4), LEFT(CELL("format", I4))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H14 G19:H21">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G4))), AND(ISNUMBER(G4), LEFT(CELL("format", G4))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A14 J4:J14"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A14 J4:J14 A19:A21 J19:J21"/>
   </dataValidations>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C4"/>
+    <hyperlink r:id="rId2" ref="C19"/>
+    <hyperlink r:id="rId3" ref="C20"/>
+    <hyperlink r:id="rId4" ref="C21"/>
+  </hyperlinks>
+  <drawing r:id="rId5"/>
+  <tableParts count="2">
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1220,15 +2170,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="29.25"/>
-    <col customWidth="1" min="2" max="2" width="16.88"/>
-    <col customWidth="1" min="4" max="4" width="15.25"/>
-    <col customWidth="1" min="9" max="9" width="12.25"/>
+    <col customWidth="1" min="1" max="1" width="24.5"/>
+    <col customWidth="1" min="2" max="2" width="17.63"/>
+    <col customWidth="1" min="3" max="3" width="15.75"/>
+    <col customWidth="1" min="4" max="4" width="19.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -1267,173 +2217,207 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="A4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
+      <c r="A5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="14"/>
       <c r="K5" s="10"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="9"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="14"/>
       <c r="K6" s="10"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="A7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="9"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="14"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="14"/>
       <c r="K8" s="10"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="17">
+        <v>45983.0</v>
+      </c>
+      <c r="F9" s="17">
+        <v>45983.0</v>
+      </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="9"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="J9" s="14"/>
       <c r="K9" s="10"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="9"/>
+      <c r="A10" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="11">
+        <v>45984.0</v>
+      </c>
+      <c r="F10" s="17">
+        <v>45985.0</v>
+      </c>
+      <c r="G10" s="17">
+        <v>45985.0</v>
+      </c>
+      <c r="H10" s="17">
+        <v>45986.0</v>
+      </c>
+      <c r="I10" s="23">
+        <v>8.5</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>94</v>
+      </c>
       <c r="K10" s="10"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="A11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="11">
+        <v>45984.0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>45984.0</v>
+      </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9"/>
+      <c r="I11" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="J11" s="14"/>
       <c r="K11" s="10"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K2"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D14">
+    <dataValidation type="list" allowBlank="1" sqref="D4:D11">
       <formula1>"Sin comenzar,En curso,Bloqueado,Completado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B4:B14">
+    <dataValidation type="list" allowBlank="1" sqref="B4:B11">
       <formula1>"Análisis,Documentación,Codificación,Validación y Verificación,Diseño,Actividades Externas,Capacitación,Pruebas"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E4:F11">
       <formula1>OR(NOT(ISERROR(DATEVALUE(E4))), AND(ISNUMBER(E4), LEFT(CELL("format", E4))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I4:I11">
       <formula1>AND(ISNUMBER(I4),(NOT(OR(NOT(ISERROR(DATEVALUE(I4))), AND(ISNUMBER(I4), LEFT(CELL("format", I4))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G4:H11">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G4))), AND(ISNUMBER(G4), LEFT(CELL("format", G4))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A14 J4:J14"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A4:A11 J4:J11"/>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C9"/>
+    <hyperlink r:id="rId2" ref="C10"/>
+    <hyperlink r:id="rId3" ref="C11"/>
+  </hyperlinks>
+  <drawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>